--- a/data/vessels/2026-10-16.xlsx
+++ b/data/vessels/2026-10-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429253" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96D72BB4-678D-4165-BCDF-9CE3DF2B7BE1}"/>
+  <xr:revisionPtr revIDLastSave="429785" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A6467D-487F-4CAD-9502-E42AF82F6418}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -161,7 +161,7 @@
     <t>SSA Marine</t>
   </si>
   <si>
-    <t>Waiting 3.4 days</t>
+    <t>Waiting 3.3 days</t>
   </si>
   <si>
     <t>Matson - HI2</t>
@@ -185,6 +185,24 @@
     <t>Ro-Ro</t>
   </si>
   <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
     <t>PNW1</t>
   </si>
   <si>
@@ -200,24 +218,6 @@
     <t>Inchcape</t>
   </si>
   <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>EB1</t>
   </si>
   <si>
@@ -260,22 +260,31 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
     <t>SALVIA ACE</t>
   </si>
   <si>
     <t>177A</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
   </si>
   <si>
     <t>FP2</t>
@@ -284,15 +293,6 @@
     <t>ONE OWL</t>
   </si>
   <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -353,6 +353,12 @@
     <t>643S</t>
   </si>
   <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -362,12 +368,6 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
     <t>EVER MACH</t>
   </si>
   <si>
@@ -554,18 +554,18 @@
     <t>FP22632C</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>NBBT0001E</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK639A</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
-  </si>
-  <si>
     <t>LAVENDER ACE</t>
   </si>
   <si>
@@ -641,6 +641,9 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
   </si>
   <si>
@@ -651,9 +654,6 @@
   </si>
   <si>
     <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -1357,19 +1357,19 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="1" t="s">
         <v>50</v>
+      </c>
+      <c r="E8" s="1">
+        <v>26164</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -1378,19 +1378,19 @@
         <v>52</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J8" s="2">
         <v>46311.625</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.708333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1401,19 +1401,19 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H9" t="s">
         <v>39</v>
@@ -1433,10 +1433,10 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
         <v>54</v>
@@ -1444,29 +1444,29 @@
       <c r="D10" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="1">
-        <v>26164</v>
+      <c r="E10" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
         <v>46311.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1629,13 +1629,13 @@
         <v>74</v>
       </c>
       <c r="F15" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
       </c>
       <c r="I15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J15" s="2">
         <v>46314.25</v>
@@ -1658,19 +1658,19 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J16" s="2">
         <v>46314.25</v>
@@ -1684,26 +1684,26 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
         <v>79</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="1">
-        <v>34</v>
-      </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
       </c>
+      <c r="H17" t="s">
+        <v>39</v>
+      </c>
       <c r="I17" t="s">
         <v>19</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>46314.625</v>
       </c>
       <c r="K17" s="2">
-        <v>46318.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L17" t="s">
         <v>32</v>
@@ -1719,26 +1719,26 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="E18" s="1">
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="G18" t="s">
         <v>25</v>
       </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
       <c r="I18" t="s">
         <v>19</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>46314.625</v>
       </c>
       <c r="K18" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L18" t="s">
         <v>32</v>
@@ -1807,7 +1807,7 @@
         <v>94</v>
       </c>
       <c r="G20" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
@@ -1880,7 +1880,7 @@
         <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2">
         <v>46315.541666666664</v>
@@ -1912,10 +1912,10 @@
         <v>46</v>
       </c>
       <c r="G23" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I23" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J23" s="2">
         <v>46316.25</v>
@@ -1970,31 +1970,34 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D25" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="E25" s="1">
+        <v>26169</v>
+      </c>
       <c r="F25" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="G25" t="s">
-        <v>25</v>
+        <v>52</v>
+      </c>
+      <c r="H25" t="s">
+        <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J25" s="2">
         <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L25" t="s">
         <v>32</v>
@@ -2005,34 +2008,31 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="1">
-        <v>26169</v>
-      </c>
-      <c r="F26" t="s">
-        <v>56</v>
-      </c>
       <c r="G26" t="s">
-        <v>57</v>
-      </c>
-      <c r="H26" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
         <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L26" t="s">
         <v>32</v>
@@ -2049,13 +2049,13 @@
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G27" t="s">
         <v>25</v>
@@ -2189,7 +2189,7 @@
         <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
         <v>25</v>
@@ -2198,7 +2198,7 @@
         <v>118</v>
       </c>
       <c r="I31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J31" s="2">
         <v>46317.666666666664</v>
@@ -2294,7 +2294,7 @@
         <v>123</v>
       </c>
       <c r="F34" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
         <v>25</v>
@@ -2303,7 +2303,7 @@
         <v>118</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J34" s="2">
         <v>46318.208333333336</v>
@@ -2338,7 +2338,7 @@
         <v>25</v>
       </c>
       <c r="I35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J35" s="2">
         <v>46318.25</v>
@@ -2358,7 +2358,7 @@
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
         <v>126</v>
@@ -2367,10 +2367,10 @@
         <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G36" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H36" t="s">
         <v>39</v>
@@ -2431,28 +2431,28 @@
         <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E38" s="1">
         <v>26168</v>
       </c>
       <c r="F38" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H38" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J38" s="2">
         <v>46318.625</v>
@@ -2519,7 +2519,7 @@
         <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J40" s="2">
         <v>46319.208333333336</v>
@@ -2548,13 +2548,13 @@
         <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
         <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J41" s="2">
         <v>46319.25</v>
@@ -2589,7 +2589,7 @@
         <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J42" s="2">
         <v>46319.25</v>
@@ -2621,13 +2621,13 @@
         <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H43" t="s">
         <v>139</v>
       </c>
       <c r="I43" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J43" s="2">
         <v>46319.25</v>
@@ -2685,10 +2685,10 @@
         <v>142</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F45" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G45" t="s">
         <v>25</v>
@@ -2793,7 +2793,7 @@
         <v>94</v>
       </c>
       <c r="G48" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
@@ -2860,7 +2860,7 @@
         <v>94</v>
       </c>
       <c r="G50" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
@@ -2883,7 +2883,7 @@
         <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D51" t="s">
         <v>154</v>
@@ -2927,13 +2927,13 @@
         <v>138</v>
       </c>
       <c r="G52" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H52" t="s">
         <v>139</v>
       </c>
       <c r="I52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J52" s="2">
         <v>46322.25</v>
@@ -2962,7 +2962,7 @@
         <v>157</v>
       </c>
       <c r="F53" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G53" t="s">
         <v>25</v>
@@ -3003,7 +3003,7 @@
         <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J54" s="2">
         <v>46323.25</v>
@@ -3049,28 +3049,28 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C56" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E56" s="1">
         <v>26173</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G56" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I56" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J56" s="2">
         <v>46323.625</v>
@@ -3105,7 +3105,7 @@
         <v>25</v>
       </c>
       <c r="I57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J57" s="2">
         <v>46323.791666666664</v>
@@ -3276,31 +3276,37 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C63" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>170</v>
+        <v>50</v>
+      </c>
+      <c r="E63" s="1">
+        <v>26172</v>
       </c>
       <c r="F63" t="s">
-        <v>46</v>
+        <v>51</v>
+      </c>
+      <c r="G63" t="s">
+        <v>52</v>
+      </c>
+      <c r="H63" t="s">
+        <v>52</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="J63" s="2">
         <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L63" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3308,37 +3314,31 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
-      </c>
-      <c r="E64" s="1">
-        <v>26172</v>
+        <v>169</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F64" t="s">
-        <v>56</v>
-      </c>
-      <c r="G64" t="s">
-        <v>57</v>
-      </c>
-      <c r="H64" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2">
         <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46326.041666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3349,7 +3349,7 @@
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D65" t="s">
         <v>169</v>
@@ -3375,13 +3375,13 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="D66" t="s">
         <v>171</v>
@@ -3390,7 +3390,7 @@
         <v>172</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -3399,7 +3399,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L66" t="s">
         <v>32</v>
@@ -3407,13 +3407,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
         <v>173</v>
@@ -3422,7 +3422,7 @@
         <v>174</v>
       </c>
       <c r="F67" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3431,7 +3431,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.916666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L67" t="s">
         <v>32</v>
@@ -3460,7 +3460,7 @@
         <v>25</v>
       </c>
       <c r="I68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J68" s="2">
         <v>46326.25</v>
@@ -3489,13 +3489,13 @@
         <v>178</v>
       </c>
       <c r="F69" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s">
         <v>25</v>
       </c>
       <c r="I69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J69" s="2">
         <v>46326.25</v>
@@ -3553,13 +3553,13 @@
         <v>178</v>
       </c>
       <c r="F71" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
       </c>
       <c r="I71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J71" s="2">
         <v>46326.791666666664</v>
@@ -3658,7 +3658,7 @@
         <v>25</v>
       </c>
       <c r="I74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J74" s="2">
         <v>46327.25</v>
@@ -3681,7 +3681,7 @@
         <v>185</v>
       </c>
       <c r="F75" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
@@ -3783,7 +3783,7 @@
         <v>25</v>
       </c>
       <c r="I78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J78" s="2">
         <v>46329.25</v>
@@ -3850,7 +3850,7 @@
         <v>25</v>
       </c>
       <c r="I80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J80" s="2">
         <v>46329.791666666664</v>
@@ -3870,7 +3870,7 @@
         <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D81" t="s">
         <v>194</v>
@@ -3902,7 +3902,7 @@
         <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D82" t="s">
         <v>194</v>
@@ -3931,19 +3931,19 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" t="s">
+        <v>104</v>
+      </c>
+      <c r="D83" t="s">
+        <v>105</v>
+      </c>
+      <c r="F83" t="s">
+        <v>51</v>
+      </c>
+      <c r="I83" t="s">
         <v>53</v>
-      </c>
-      <c r="C83" t="s">
-        <v>107</v>
-      </c>
-      <c r="D83" t="s">
-        <v>108</v>
-      </c>
-      <c r="F83" t="s">
-        <v>56</v>
-      </c>
-      <c r="I83" t="s">
-        <v>58</v>
       </c>
       <c r="J83" s="2">
         <v>46330.625</v>
@@ -4085,7 +4085,7 @@
         <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C88" t="s">
         <v>21</v>
@@ -4094,7 +4094,7 @@
         <v>200</v>
       </c>
       <c r="E88" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
         <v>99</v>
@@ -4103,7 +4103,7 @@
         <v>25</v>
       </c>
       <c r="I88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J88" s="2">
         <v>46331.25</v>
@@ -4120,7 +4120,7 @@
         <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C89" t="s">
         <v>21</v>
@@ -4128,20 +4128,17 @@
       <c r="D89" t="s">
         <v>201</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>202</v>
+      <c r="E89" s="1">
+        <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G89" t="s">
         <v>25</v>
       </c>
-      <c r="H89" t="s">
-        <v>203</v>
-      </c>
       <c r="I89" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J89" s="2">
         <v>46331.25</v>
@@ -4164,19 +4161,22 @@
         <v>21</v>
       </c>
       <c r="D90" t="s">
-        <v>204</v>
-      </c>
-      <c r="E90" s="1">
-        <v>10</v>
+        <v>202</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F90" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G90" t="s">
         <v>25</v>
       </c>
+      <c r="H90" t="s">
+        <v>204</v>
+      </c>
       <c r="I90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J90" s="2">
         <v>46331.25</v>
@@ -4295,22 +4295,19 @@
         <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>201</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
+      </c>
+      <c r="E94" s="1">
+        <v>10</v>
       </c>
       <c r="F94" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="G94" t="s">
         <v>25</v>
       </c>
-      <c r="H94" t="s">
-        <v>203</v>
-      </c>
       <c r="I94" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J94" s="2">
         <v>46331.791666666664</v>
@@ -4327,25 +4324,28 @@
         <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="C95" t="s">
         <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>200</v>
-      </c>
-      <c r="E95" s="1">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s">
         <v>25</v>
       </c>
+      <c r="H95" t="s">
+        <v>204</v>
+      </c>
       <c r="I95" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J95" s="2">
         <v>46331.791666666664</v>
@@ -4362,16 +4362,16 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C96" t="s">
         <v>21</v>
       </c>
       <c r="D96" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E96" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F96" t="s">
         <v>99</v>
@@ -4380,7 +4380,7 @@
         <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J96" s="2">
         <v>46331.791666666664</v>
@@ -4464,7 +4464,7 @@
         <v>211</v>
       </c>
       <c r="F99" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
@@ -4490,7 +4490,7 @@
         <v>211</v>
       </c>
       <c r="F100" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -4510,16 +4510,16 @@
         <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C101" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D101" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F101" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4543,12 +4543,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4686,7 +4694,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4695,26 +4703,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
--- a/data/vessels/2026-10-16.xlsx
+++ b/data/vessels/2026-10-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429785" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A6467D-487F-4CAD-9502-E42AF82F6418}"/>
+  <xr:revisionPtr revIDLastSave="430320" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A075781E-5D41-48C6-9976-7017ECE4E80D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="212">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,6 +83,27 @@
     <t>T18</t>
   </si>
   <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -98,72 +119,48 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
-    <t>Container</t>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>CAPE TAINARO</t>
+  </si>
+  <si>
+    <t>MC642R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
   </si>
   <si>
     <t>At berth</t>
   </si>
   <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>CAPE TAINARO</t>
-  </si>
-  <si>
-    <t>MC642R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Tacoma</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Waiting 3.3 days</t>
-  </si>
-  <si>
     <t>Matson - HI2</t>
   </si>
   <si>
@@ -203,6 +200,12 @@
     <t>Multipurpose</t>
   </si>
   <si>
+    <t>Waiting 2.7 days</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
     <t>PNW1</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
     <t>Inchcape</t>
   </si>
   <si>
-    <t>EB1</t>
-  </si>
-  <si>
     <t>Husky</t>
   </si>
   <si>
@@ -260,6 +260,15 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
     <t>THEMISA</t>
   </si>
   <si>
@@ -269,13 +278,10 @@
     <t>Wallenius</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
   </si>
   <si>
     <t>SM QINGDAO</t>
@@ -287,12 +293,6 @@
     <t>SM Line</t>
   </si>
   <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -437,18 +437,18 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
     <t>ARC HONOR</t>
   </si>
   <si>
     <t>ED616</t>
   </si>
   <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
     <t>LIBERTY PEACE</t>
   </si>
   <si>
@@ -488,7 +488,7 @@
     <t>YM WEALTH</t>
   </si>
   <si>
-    <t>PN32637W</t>
+    <t>193E</t>
   </si>
   <si>
     <t>MSC IVANA</t>
@@ -500,7 +500,7 @@
     <t>YM PLUM</t>
   </si>
   <si>
-    <t>PN12640E</t>
+    <t>197E</t>
   </si>
   <si>
     <t>YM TUTORIAL</t>
@@ -551,7 +551,7 @@
     <t>ONE SYNERGY</t>
   </si>
   <si>
-    <t>FP22632C</t>
+    <t>OYNT0002E</t>
   </si>
   <si>
     <t>ONE DURBAN</t>
@@ -563,7 +563,13 @@
     <t>MSC SOLA</t>
   </si>
   <si>
-    <t>UK639A</t>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
   </si>
   <si>
     <t>LAVENDER ACE</t>
@@ -572,16 +578,10 @@
     <t>123A</t>
   </si>
   <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
-    <t>PN32640W</t>
+    <t>HFWT0172E</t>
   </si>
   <si>
     <t>Not Specified</t>
@@ -590,6 +590,9 @@
     <t>CYPRESS</t>
   </si>
   <si>
+    <t>CPN060S19</t>
+  </si>
+  <si>
     <t>EUROPEAN HIGHWAY</t>
   </si>
   <si>
@@ -602,13 +605,13 @@
     <t>ONE MAJESTY</t>
   </si>
   <si>
-    <t>PN12641W</t>
+    <t>26E</t>
   </si>
   <si>
     <t>EVER SMILE</t>
   </si>
   <si>
-    <t>495E</t>
+    <t>495-136E</t>
   </si>
   <si>
     <t>SWIFT ACE</t>
@@ -626,7 +629,7 @@
     <t>ONE FANTASTIC</t>
   </si>
   <si>
-    <t>FP22633B</t>
+    <t>FP22633C</t>
   </si>
   <si>
     <t>BUDAPEST EXPRESS</t>
@@ -641,21 +644,21 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
   </si>
   <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
     <t>MSC SABRINA</t>
   </si>
   <si>
@@ -663,9 +666,6 @@
   </si>
   <si>
     <t>CORNEILLE</t>
-  </si>
-  <si>
-    <t>OILT0014E</t>
   </si>
   <si>
     <t>WESTWOOD COLUMBIA</t>
@@ -747,10 +747,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L101" totalsRowShown="0">
-  <autoFilter ref="A1:L101" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L101">
-    <sortCondition ref="J2:J101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
+  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
+    <sortCondition ref="J2:J102"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1087,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1165,10 +1165,10 @@
         <v>19</v>
       </c>
       <c r="J2" s="2">
-        <v>46310.25</v>
+        <v>46310.583333333336</v>
       </c>
       <c r="K2" s="2">
-        <v>46311.708333333336</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L2" t="s">
         <v>20</v>
@@ -1182,19 +1182,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -1203,10 +1203,10 @@
         <v>46310.583333333336</v>
       </c>
       <c r="K3" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1214,19 +1214,19 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -1235,159 +1235,153 @@
         <v>19</v>
       </c>
       <c r="J4" s="2">
-        <v>46310.708333333336</v>
+        <v>46310.583333333336</v>
       </c>
       <c r="K4" s="2">
-        <v>46312.291666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
       </c>
       <c r="J5" s="2">
-        <v>46311.104166666664</v>
+        <v>46310.583333333336</v>
       </c>
       <c r="K5" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.708333333336</v>
       </c>
       <c r="L5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46311.333333333336</v>
+        <v>46310.708333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46312.125</v>
+        <v>46312.291666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="2">
+        <v>46311.104166666664</v>
+      </c>
+      <c r="K7" s="2">
+        <v>46311.916666666664</v>
+      </c>
+      <c r="L7" t="s">
         <v>39</v>
-      </c>
-      <c r="I7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="2">
-        <v>46311.541666666664</v>
-      </c>
-      <c r="K7" s="2">
-        <v>46312.083333333336</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="1">
-        <v>26164</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46311.625</v>
+        <v>46311.333333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -1395,107 +1389,107 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="J9" s="2">
-        <v>46311.625</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K9" s="2">
-        <v>46312.708333333336</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="E10" s="1">
+        <v>26164</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J10" s="2">
         <v>46311.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46312.708333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" t="s">
         <v>45</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+      <c r="I11" t="s">
         <v>46</v>
-      </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" t="s">
-        <v>47</v>
       </c>
       <c r="J11" s="2">
         <v>46312.125</v>
@@ -1504,77 +1498,80 @@
         <v>46312.666666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>59</v>
+      </c>
+      <c r="H12" t="s">
+        <v>38</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46312.3125</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46314.75</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46312.541666666664</v>
+        <v>46312.3125</v>
       </c>
       <c r="K13" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L13" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1585,63 +1582,63 @@
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46312.75</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46313.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L14" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46314.25</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K15" s="2">
-        <v>46314.75</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L15" t="s">
         <v>26</v>
@@ -1649,28 +1646,28 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J16" s="2">
         <v>46314.25</v>
@@ -1679,65 +1676,65 @@
         <v>46314.75</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J17" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46315.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L17" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
         <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E18" s="1">
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
         <v>19</v>
@@ -1749,144 +1746,144 @@
         <v>46318.75</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>89</v>
+        <v>18</v>
+      </c>
+      <c r="H19" t="s">
+        <v>38</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K19" s="2">
-        <v>46316.791666666664</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46315.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L20" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="I21" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.25</v>
       </c>
       <c r="K21" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2</v>
+        <v>96</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46315.541666666664</v>
+        <v>46315.291666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L22" t="s">
         <v>26</v>
@@ -1894,153 +1891,153 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E23" s="1">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="I23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J23" s="2">
-        <v>46316.25</v>
+        <v>46315.541666666664</v>
       </c>
       <c r="K23" s="2">
         <v>46316.75</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="E24" s="1">
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
-      </c>
-      <c r="H24" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L24" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" t="s">
         <v>33</v>
       </c>
-      <c r="B25" t="s">
-        <v>48</v>
-      </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="1">
-        <v>26169</v>
+        <v>102</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F25" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G25" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
-        <v>46316.625</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46317.041666666664</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="E26" s="1">
+        <v>26169</v>
       </c>
       <c r="F26" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="H26" t="s">
+        <v>51</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J26" s="2">
         <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" t="s">
         <v>60</v>
@@ -2058,7 +2055,7 @@
         <v>108</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I27" t="s">
         <v>19</v>
@@ -2070,74 +2067,74 @@
         <v>46319.75</v>
       </c>
       <c r="L27" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>60</v>
+      </c>
+      <c r="C28" t="s">
+        <v>61</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G28" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K28" s="2">
-        <v>46318.708333333336</v>
+        <v>46319.75</v>
       </c>
       <c r="L28" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.25</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L29" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2145,63 +2142,60 @@
         <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="G30" t="s">
+        <v>72</v>
       </c>
       <c r="I30" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.25</v>
       </c>
       <c r="K30" s="2">
         <v>46318.166666666664</v>
       </c>
       <c r="L30" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
       <c r="I31" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2">
-        <v>46317.666666666664</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K31" s="2">
         <v>46318.166666666664</v>
@@ -2212,66 +2206,69 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>78</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" t="s">
+        <v>118</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.927777777775</v>
+        <v>46317.666666666664</v>
       </c>
       <c r="K32" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>120</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" t="s">
-        <v>38</v>
-      </c>
-      <c r="H33" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="I33" t="s">
         <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46318.104166666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -2279,186 +2276,183 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>43</v>
-      </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F34" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H34" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="I34" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.208333333336</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K34" s="2">
-        <v>46319.125</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H35" t="s">
+        <v>118</v>
       </c>
       <c r="I35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J35" s="2">
-        <v>46318.25</v>
+        <v>46318.208333333336</v>
       </c>
       <c r="K35" s="2">
-        <v>46318.75</v>
+        <v>46319.125</v>
       </c>
       <c r="L35" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
-      </c>
-      <c r="H36" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J36" s="2">
         <v>46318.25</v>
       </c>
       <c r="K36" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L36" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F37" t="s">
+        <v>58</v>
+      </c>
+      <c r="G37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H37" t="s">
         <v>38</v>
       </c>
-      <c r="G37" t="s">
-        <v>38</v>
-      </c>
-      <c r="H37" t="s">
-        <v>39</v>
-      </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46319.125</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
         <v>33</v>
       </c>
-      <c r="B38" t="s">
-        <v>48</v>
-      </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="1">
-        <v>26168</v>
+        <v>128</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="F38" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="G38" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="H38" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I38" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.625</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L38" t="s">
         <v>26</v>
@@ -2466,66 +2460,69 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D39" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>129</v>
+        <v>49</v>
+      </c>
+      <c r="E39" s="1">
+        <v>26168</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="G39" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" t="s">
+        <v>51</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.625</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" t="s">
         <v>33</v>
       </c>
-      <c r="B40" t="s">
-        <v>59</v>
-      </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
-      </c>
-      <c r="E40" s="1">
-        <v>4</v>
+        <v>130</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
-      </c>
-      <c r="G40" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I40" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J40" s="2">
-        <v>46319.208333333336</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -2533,63 +2530,63 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>132</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4</v>
       </c>
       <c r="F41" t="s">
+        <v>99</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" t="s">
         <v>75</v>
       </c>
-      <c r="G41" t="s">
-        <v>25</v>
-      </c>
-      <c r="I41" t="s">
-        <v>76</v>
-      </c>
       <c r="J41" s="2">
-        <v>46319.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K41" s="2">
         <v>46319.75</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
         <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J42" s="2">
         <v>46319.25</v>
@@ -2598,80 +2595,80 @@
         <v>46322.75</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
-      </c>
-      <c r="H43" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J43" s="2">
         <v>46319.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G44" t="s">
-        <v>25</v>
+        <v>59</v>
+      </c>
+      <c r="H44" t="s">
+        <v>139</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.291666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46320.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2679,267 +2676,267 @@
         <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
+        <v>95</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="F45" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
-      </c>
-      <c r="H45" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.625</v>
+        <v>46319.291666666664</v>
       </c>
       <c r="K45" s="2">
-        <v>46320.166666666664</v>
+        <v>46320.75</v>
       </c>
       <c r="L45" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
-      </c>
-      <c r="C46" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="F46" t="s">
-        <v>88</v>
+        <v>83</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" t="s">
+        <v>38</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46320</v>
+        <v>46319.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46322</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46320.21875</v>
+        <v>46320</v>
       </c>
       <c r="K47" s="2">
-        <v>46324.59375</v>
+        <v>46322</v>
       </c>
       <c r="L47" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="D48" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F48" t="s">
-        <v>94</v>
-      </c>
-      <c r="G48" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.208333333336</v>
+        <v>46320.21875</v>
       </c>
       <c r="K48" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L48" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>94</v>
+      </c>
+      <c r="G49" t="s">
+        <v>59</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K49" s="2">
-        <v>46323.21875</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F50" t="s">
-        <v>94</v>
-      </c>
-      <c r="G50" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L50" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D51" t="s">
-        <v>154</v>
-      </c>
-      <c r="E51" s="1">
-        <v>21</v>
+        <v>152</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F51" t="s">
         <v>94</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
+        <v>79</v>
+      </c>
+      <c r="D52" t="s">
+        <v>154</v>
+      </c>
+      <c r="E52" s="1">
         <v>21</v>
       </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
       <c r="F52" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
-      </c>
-      <c r="H52" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46322.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K52" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -2947,69 +2944,69 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>59</v>
+      </c>
+      <c r="H53" t="s">
+        <v>139</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L53" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D54" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F54" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K54" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L54" t="s">
         <v>26</v>
@@ -3017,101 +3014,101 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>158</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F55" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L55" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
+        <v>32</v>
+      </c>
+      <c r="B56" t="s">
         <v>33</v>
       </c>
-      <c r="B56" t="s">
-        <v>48</v>
-      </c>
       <c r="C56" t="s">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="D56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E56" s="1">
-        <v>26173</v>
+        <v>35</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
-      </c>
-      <c r="G56" t="s">
-        <v>52</v>
-      </c>
-      <c r="H56" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I56" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D57" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>159</v>
+        <v>105</v>
+      </c>
+      <c r="E57" s="1">
+        <v>26173</v>
       </c>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G57" t="s">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="H57" t="s">
+        <v>51</v>
       </c>
       <c r="I57" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L57" t="s">
         <v>26</v>
@@ -3119,63 +3116,66 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="C58" t="s">
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F58" t="s">
-        <v>88</v>
+        <v>45</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J58" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L58" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F59" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46324.647916666669</v>
+        <v>46324</v>
       </c>
       <c r="K59" s="2">
-        <v>46326.147916666669</v>
+        <v>46326</v>
       </c>
       <c r="L59" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3183,31 +3183,31 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.003472222219</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K60" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L60" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3215,95 +3215,89 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L61" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D62" t="s">
-        <v>102</v>
+        <v>167</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K62" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L62" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" t="s">
         <v>33</v>
       </c>
-      <c r="B63" t="s">
-        <v>48</v>
-      </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
-      </c>
-      <c r="E63" s="1">
-        <v>26172</v>
+        <v>102</v>
       </c>
       <c r="F63" t="s">
-        <v>51</v>
-      </c>
-      <c r="G63" t="s">
-        <v>52</v>
-      </c>
-      <c r="H63" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K63" s="2">
-        <v>46326.041666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
@@ -3311,13 +3305,13 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B64" t="s">
         <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D64" t="s">
         <v>169</v>
@@ -3326,7 +3320,7 @@
         <v>170</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I64" t="s">
         <v>19</v>
@@ -3338,18 +3332,18 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B65" t="s">
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
         <v>169</v>
@@ -3358,7 +3352,7 @@
         <v>170</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
@@ -3370,59 +3364,65 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>172</v>
+        <v>49</v>
+      </c>
+      <c r="E66" s="1">
+        <v>26172</v>
       </c>
       <c r="F66" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="G66" t="s">
+        <v>51</v>
+      </c>
+      <c r="H66" t="s">
+        <v>51</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J66" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K66" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C67" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F67" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3431,42 +3431,39 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F68" t="s">
-        <v>46</v>
-      </c>
-      <c r="G68" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J68" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -3474,28 +3471,28 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F69" t="s">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
+      </c>
+      <c r="I69" t="s">
         <v>75</v>
-      </c>
-      <c r="G69" t="s">
-        <v>25</v>
-      </c>
-      <c r="I69" t="s">
-        <v>76</v>
       </c>
       <c r="J69" s="2">
         <v>46326.25</v>
@@ -3504,68 +3501,68 @@
         <v>46326.75</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>177</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F70" t="s">
-        <v>38</v>
+        <v>45</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K70" s="2">
         <v>46326.75</v>
       </c>
       <c r="L70" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
+        <v>32</v>
+      </c>
+      <c r="B71" t="s">
         <v>33</v>
       </c>
-      <c r="B71" t="s">
-        <v>43</v>
-      </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>178</v>
+        <v>41</v>
       </c>
       <c r="F71" t="s">
-        <v>75</v>
-      </c>
-      <c r="G71" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I71" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K71" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -3573,98 +3570,98 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F72" t="s">
-        <v>181</v>
+        <v>78</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L72" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="C73" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="D73" t="s">
-        <v>182</v>
-      </c>
-      <c r="E73" s="1">
-        <v>69</v>
+        <v>179</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F73" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L73" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D74" t="s">
+        <v>182</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="F74" t="s">
-        <v>46</v>
-      </c>
-      <c r="G74" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46327.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -3672,124 +3669,124 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
       </c>
       <c r="D75" t="s">
+        <v>184</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>185</v>
       </c>
       <c r="F75" t="s">
-        <v>81</v>
+        <v>45</v>
+      </c>
+      <c r="G75" t="s">
+        <v>18</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J75" s="2">
+        <v>46327.25</v>
+      </c>
+      <c r="K75" s="2">
         <v>46327.708333333336</v>
       </c>
-      <c r="K75" s="2">
-        <v>46328.833333333336</v>
-      </c>
       <c r="L75" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>90</v>
-      </c>
-      <c r="C76" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
         <v>186</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="I76" t="s">
         <v>19</v>
       </c>
       <c r="J76" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K76" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L76" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D77" t="s">
+        <v>187</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="F77" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46329</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K77" s="2">
-        <v>46330</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L77" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="D78" t="s">
+        <v>189</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="F78" t="s">
-        <v>46</v>
-      </c>
-      <c r="G78" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="I78" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46329.25</v>
+        <v>46329</v>
       </c>
       <c r="K78" s="2">
-        <v>46329.75</v>
+        <v>46330</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -3797,66 +3794,66 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D79" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="F79" t="s">
-        <v>181</v>
+        <v>45</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J79" s="2">
-        <v>46329.333333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K79" s="2">
-        <v>46332.625</v>
+        <v>46329.75</v>
       </c>
       <c r="L79" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C80" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D80" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
-      </c>
-      <c r="G80" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="I80" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.791666666664</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46330.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L80" t="s">
         <v>26</v>
@@ -3864,54 +3861,57 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C81" t="s">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F81" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="G81" t="s">
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J81" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46334</v>
+        <v>46330.75</v>
       </c>
       <c r="L81" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B82" t="s">
         <v>60</v>
       </c>
       <c r="C82" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
@@ -3923,73 +3923,73 @@
         <v>46334</v>
       </c>
       <c r="L82" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D83" t="s">
-        <v>105</v>
+        <v>195</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F83" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I83" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K83" s="2">
-        <v>46331.125</v>
+        <v>46334</v>
       </c>
       <c r="L83" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C84" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D84" t="s">
-        <v>196</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="F84" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K84" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L84" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
         <v>60</v>
@@ -3998,10 +3998,10 @@
         <v>61</v>
       </c>
       <c r="D85" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F85" t="s">
         <v>181</v>
@@ -4016,100 +4016,97 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L85" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="C86" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D86" t="s">
-        <v>130</v>
+        <v>197</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F86" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K86" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L86" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C87" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="D87" t="s">
-        <v>198</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>199</v>
+        <v>130</v>
       </c>
       <c r="F87" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.75</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K87" s="2">
-        <v>46332.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L87" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D88" t="s">
+        <v>199</v>
+      </c>
+      <c r="E88" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E88" s="1">
-        <v>10</v>
-      </c>
       <c r="F88" t="s">
-        <v>99</v>
-      </c>
-      <c r="G88" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J88" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K88" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
@@ -4117,28 +4114,31 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B89" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D89" t="s">
         <v>201</v>
       </c>
-      <c r="E89" s="1">
-        <v>1</v>
+      <c r="E89" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F89" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="G89" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H89" t="s">
+        <v>203</v>
       </c>
       <c r="I89" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J89" s="2">
         <v>46331.25</v>
@@ -4147,36 +4147,33 @@
         <v>46331.75</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>202</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
+      </c>
+      <c r="E90" s="1">
+        <v>1</v>
       </c>
       <c r="F90" t="s">
+        <v>99</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
+      </c>
+      <c r="I90" t="s">
         <v>75</v>
-      </c>
-      <c r="G90" t="s">
-        <v>25</v>
-      </c>
-      <c r="H90" t="s">
-        <v>204</v>
-      </c>
-      <c r="I90" t="s">
-        <v>76</v>
       </c>
       <c r="J90" s="2">
         <v>46331.25</v>
@@ -4185,76 +4182,79 @@
         <v>46331.75</v>
       </c>
       <c r="L90" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C91" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
         <v>205</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>206</v>
+      <c r="E91" s="1">
+        <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>31</v>
+        <v>99</v>
+      </c>
+      <c r="G91" t="s">
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L91" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="C92" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="D92" t="s">
+        <v>206</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="F92" t="s">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="I92" t="s">
         <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L92" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B93" t="s">
         <v>90</v>
@@ -4263,10 +4263,10 @@
         <v>91</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="F93" t="s">
         <v>181</v>
@@ -4281,39 +4281,36 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L93" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B94" t="s">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="D94" t="s">
-        <v>200</v>
-      </c>
-      <c r="E94" s="1">
-        <v>10</v>
+        <v>208</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F94" t="s">
-        <v>99</v>
-      </c>
-      <c r="G94" t="s">
-        <v>25</v>
+        <v>181</v>
       </c>
       <c r="I94" t="s">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K94" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -4321,31 +4318,28 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
+      </c>
+      <c r="E95" s="1">
+        <v>10</v>
       </c>
       <c r="F95" t="s">
+        <v>99</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
         <v>75</v>
-      </c>
-      <c r="G95" t="s">
-        <v>25</v>
-      </c>
-      <c r="H95" t="s">
-        <v>204</v>
-      </c>
-      <c r="I95" t="s">
-        <v>76</v>
       </c>
       <c r="J95" s="2">
         <v>46331.791666666664</v>
@@ -4354,33 +4348,36 @@
         <v>46332.75</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s">
         <v>201</v>
       </c>
-      <c r="E96" s="1">
-        <v>1</v>
+      <c r="E96" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F96" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H96" t="s">
+        <v>203</v>
       </c>
       <c r="I96" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J96" s="2">
         <v>46331.791666666664</v>
@@ -4389,94 +4386,103 @@
         <v>46332.75</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>209</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>210</v>
+        <v>204</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>17</v>
+        <v>99</v>
+      </c>
+      <c r="G97" t="s">
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J97" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L97" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="D98" t="s">
-        <v>36</v>
+        <v>209</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F98" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L98" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="C99" t="s">
+        <v>34</v>
       </c>
       <c r="D99" t="s">
-        <v>211</v>
+        <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>81</v>
+        <v>37</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.375</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46333.5</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L99" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4490,7 +4496,7 @@
         <v>211</v>
       </c>
       <c r="F100" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
@@ -4502,36 +4508,62 @@
         <v>46333.5</v>
       </c>
       <c r="L100" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" t="s">
+        <v>211</v>
+      </c>
+      <c r="F101" t="s">
+        <v>83</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" s="2">
+        <v>46332.375</v>
+      </c>
+      <c r="K101" s="2">
+        <v>46333.5</v>
+      </c>
+      <c r="L101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102" t="s">
+        <v>47</v>
+      </c>
+      <c r="C102" t="s">
         <v>48</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D102" t="s">
         <v>49</v>
       </c>
-      <c r="D101" t="s">
+      <c r="F102" t="s">
         <v>50</v>
       </c>
-      <c r="F101" t="s">
-        <v>51</v>
-      </c>
-      <c r="I101" t="s">
-        <v>19</v>
-      </c>
-      <c r="J101" s="2">
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" s="2">
         <v>46332.541666666664</v>
       </c>
-      <c r="K101" s="2">
+      <c r="K102" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="L101" t="s">
-        <v>26</v>
+      <c r="L102" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4543,6 +4575,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4550,13 +4591,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4694,27 +4735,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-16.xlsx
+++ b/data/vessels/2026-10-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430320" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A075781E-5D41-48C6-9976-7017ECE4E80D}"/>
+  <xr:revisionPtr revIDLastSave="430755" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74E3B2B9-F99C-470E-86DC-67C9D349F6AA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="212">
   <si>
     <t>Harbor</t>
   </si>
@@ -122,6 +122,30 @@
     <t>In transit</t>
   </si>
   <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>641S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>At berth</t>
+  </si>
+  <si>
     <t>T5</t>
   </si>
   <si>
@@ -137,30 +161,6 @@
     <t>MSC</t>
   </si>
   <si>
-    <t>Tacoma</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>At berth</t>
-  </si>
-  <si>
     <t>Matson - HI2</t>
   </si>
   <si>
@@ -260,22 +260,40 @@
     <t>COSCO SHIPPING LINES</t>
   </si>
   <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
     <t>SALVIA ACE</t>
   </si>
   <si>
     <t>177A</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
   </si>
   <si>
     <t>FP2</t>
@@ -284,15 +302,6 @@
     <t>ONE OWL</t>
   </si>
   <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
     <t>PCT</t>
   </si>
   <si>
@@ -311,6 +320,12 @@
     <t>BEN LINES</t>
   </si>
   <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -326,21 +341,12 @@
     <t>Yang Ming</t>
   </si>
   <si>
-    <t>Chinook</t>
-  </si>
-  <si>
     <t>MSC DENISSE X</t>
   </si>
   <si>
     <t>UK641R</t>
   </si>
   <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
     <t>T7</t>
   </si>
   <si>
@@ -353,19 +359,28 @@
     <t>643S</t>
   </si>
   <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
     <t>Tote - AK1</t>
   </si>
   <si>
     <t>MIDNIGHT SUN</t>
   </si>
   <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
   </si>
   <si>
     <t>EVER MACH</t>
@@ -377,120 +392,105 @@
     <t>BEN LINE</t>
   </si>
   <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>193E</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN040S19</t>
+  </si>
+  <si>
     <t>COSCO VENICE</t>
   </si>
   <si>
     <t>081N/081S</t>
   </si>
   <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>193E</t>
-  </si>
-  <si>
     <t>MSC IVANA</t>
   </si>
   <si>
@@ -566,18 +566,18 @@
     <t>UK643R</t>
   </si>
   <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
     <t>KW665</t>
   </si>
   <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
@@ -653,10 +653,10 @@
     <t>Jones Stevedoring Co</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -747,10 +747,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
-  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
-    <sortCondition ref="J2:J102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L103" totalsRowShown="0">
+  <autoFilter ref="A1:L103" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L103">
+    <sortCondition ref="J2:J103"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1087,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1281,83 +1281,83 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>32</v>
+      </c>
+      <c r="H6" t="s">
+        <v>33</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46310.708333333336</v>
+        <v>46311.104166666664</v>
       </c>
       <c r="K6" s="2">
-        <v>46312.291666666664</v>
+        <v>46311.916666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46311.104166666664</v>
+        <v>46311.25</v>
       </c>
       <c r="K7" s="2">
-        <v>46311.916666666664</v>
+        <v>46312.166666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>40</v>
@@ -1366,13 +1366,13 @@
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
         <v>42</v>
@@ -1410,7 +1410,7 @@
         <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I9" t="s">
         <v>46</v>
@@ -1427,7 +1427,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>54</v>
@@ -1486,7 +1486,7 @@
         <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
         <v>46</v>
@@ -1524,7 +1524,7 @@
         <v>59</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>60</v>
@@ -1646,42 +1646,42 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2">
-        <v>46314.25</v>
+        <v>46313.25</v>
       </c>
       <c r="K16" s="2">
         <v>46314.75</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
         <v>54</v>
@@ -1702,7 +1702,7 @@
         <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J17" s="2">
         <v>46314.25</v>
@@ -1716,19 +1716,19 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="1">
-        <v>34</v>
+      <c r="E18" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="F18" t="s">
         <v>45</v>
@@ -1737,16 +1737,16 @@
         <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J18" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46318.75</v>
+        <v>46314.75</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1757,19 +1757,19 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
         <v>85</v>
@@ -1797,23 +1797,23 @@
       <c r="D20" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>87</v>
+      <c r="E20" s="1">
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="G20" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K20" s="2">
-        <v>46316.791666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -1821,34 +1821,34 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
         <v>92</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" t="s">
-        <v>59</v>
-      </c>
       <c r="I21" t="s">
         <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46315.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.791666666664</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -1856,180 +1856,177 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
         <v>18</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J22" s="2">
-        <v>46315.291666666664</v>
+        <v>46315.541666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2</v>
       </c>
       <c r="F23" t="s">
         <v>99</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="I23" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46315.541666666664</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>100</v>
       </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="1">
-        <v>63</v>
-      </c>
       <c r="F24" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.25</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="E25" s="1">
+        <v>63</v>
+      </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G25" t="s">
-        <v>37</v>
-      </c>
-      <c r="H25" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J25" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K25" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="1">
-        <v>26169</v>
-      </c>
-      <c r="F26" t="s">
-        <v>50</v>
-      </c>
       <c r="G26" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I26" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46316.625</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46317.041666666664</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -2037,7 +2034,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
         <v>60</v>
@@ -2072,7 +2069,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>60</v>
@@ -2107,31 +2104,37 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>109</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="E29" s="1">
+        <v>26169</v>
+      </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
-        <v>111</v>
+        <v>51</v>
+      </c>
+      <c r="H29" t="s">
+        <v>51</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.708333333336</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -2139,48 +2142,48 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" t="s">
         <v>113</v>
       </c>
-      <c r="F30" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" t="s">
-        <v>72</v>
-      </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J30" s="2">
-        <v>46317.25</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K30" s="2">
-        <v>46318.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
         <v>114</v>
@@ -2189,16 +2192,19 @@
         <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>91</v>
+      </c>
+      <c r="G31" t="s">
+        <v>116</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K31" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L31" t="s">
         <v>26</v>
@@ -2206,104 +2212,101 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.666666666664</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K32" s="2">
         <v>46318.166666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" t="s">
         <v>119</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
         <v>120</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F33" t="s">
-        <v>24</v>
+      <c r="G33" t="s">
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J33" s="2">
-        <v>46317.927777777775</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.969444444447</v>
+        <v>46320.75</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>119</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="G34" t="s">
-        <v>37</v>
-      </c>
-      <c r="H34" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.104166666664</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K34" s="2">
-        <v>46318.916666666664</v>
+        <v>46320.75</v>
       </c>
       <c r="L34" t="s">
         <v>20</v>
@@ -2311,19 +2314,19 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" t="s">
         <v>78</v>
@@ -2332,16 +2335,16 @@
         <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I35" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J35" s="2">
-        <v>46318.208333333336</v>
+        <v>46317.666666666664</v>
       </c>
       <c r="K35" s="2">
-        <v>46319.125</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -2349,180 +2352,177 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F36" t="s">
-        <v>45</v>
-      </c>
-      <c r="G36" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I36" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46318.25</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K36" s="2">
-        <v>46318.75</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="H37" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.25</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K37" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G38" t="s">
-        <v>37</v>
-      </c>
-      <c r="H38" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.125</v>
+        <v>46318.75</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="1">
-        <v>26168</v>
+        <v>128</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H39" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="I39" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.625</v>
+        <v>46318.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D40" t="s">
         <v>130</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="G40" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" t="s">
+        <v>33</v>
       </c>
       <c r="I40" t="s">
         <v>19</v>
       </c>
       <c r="J40" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.125</v>
       </c>
       <c r="L40" t="s">
         <v>26</v>
@@ -2530,77 +2530,77 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="E41" s="1">
-        <v>4</v>
+        <v>26168</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>51</v>
+      </c>
+      <c r="H41" t="s">
+        <v>51</v>
       </c>
       <c r="I41" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.208333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.75</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D42" t="s">
         <v>132</v>
       </c>
-      <c r="E42" s="1">
-        <v>1</v>
+      <c r="E42" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F42" t="s">
-        <v>133</v>
-      </c>
-      <c r="G42" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I42" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K42" s="2">
-        <v>46322.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -2609,22 +2609,22 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
+      </c>
+      <c r="E43" s="1">
+        <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G43" t="s">
         <v>18</v>
       </c>
       <c r="I43" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K43" s="2">
         <v>46319.75</v>
@@ -2635,37 +2635,34 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s">
-        <v>59</v>
-      </c>
-      <c r="H44" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="I44" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J44" s="2">
         <v>46319.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L44" t="s">
         <v>20</v>
@@ -2673,37 +2670,40 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F45" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="H45" t="s">
+        <v>139</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.291666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46320.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2714,19 +2714,19 @@
         <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
@@ -2743,31 +2743,34 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B47" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="F47" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="G47" t="s">
+        <v>59</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46320</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K47" s="2">
-        <v>46322</v>
+        <v>46321.75</v>
       </c>
       <c r="L47" t="s">
         <v>26</v>
@@ -2775,31 +2778,31 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="F48" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46320.21875</v>
+        <v>46320</v>
       </c>
       <c r="K48" s="2">
-        <v>46324.59375</v>
+        <v>46322</v>
       </c>
       <c r="L48" t="s">
         <v>26</v>
@@ -2807,34 +2810,31 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" t="s">
+        <v>146</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D49" t="s">
-        <v>148</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="F49" t="s">
-        <v>94</v>
-      </c>
-      <c r="G49" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.208333333336</v>
+        <v>46320.21875</v>
       </c>
       <c r="K49" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L49" t="s">
         <v>26</v>
@@ -2845,28 +2845,31 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>71</v>
+      </c>
+      <c r="G50" t="s">
+        <v>72</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.21875</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L50" t="s">
         <v>26</v>
@@ -2874,34 +2877,31 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>94</v>
-      </c>
-      <c r="G51" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L51" t="s">
         <v>26</v>
@@ -2909,34 +2909,34 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
-      </c>
-      <c r="E52" s="1">
-        <v>21</v>
+        <v>152</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F52" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G52" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46321.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L52" t="s">
         <v>26</v>
@@ -2944,133 +2944,139 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="E53" s="1">
+        <v>21</v>
       </c>
       <c r="F53" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="G53" t="s">
-        <v>59</v>
-      </c>
-      <c r="H53" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L53" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F54" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>59</v>
+      </c>
+      <c r="H54" t="s">
+        <v>139</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J54" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F55" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="G55" t="s">
         <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L55" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
+        <v>158</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F56" t="s">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K56" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L56" t="s">
         <v>20</v>
@@ -3078,133 +3084,130 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>28</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" t="s">
+        <v>30</v>
+      </c>
+      <c r="F57" t="s">
         <v>32</v>
       </c>
-      <c r="B57" t="s">
-        <v>47</v>
-      </c>
-      <c r="C57" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" t="s">
-        <v>105</v>
-      </c>
-      <c r="E57" s="1">
-        <v>26173</v>
-      </c>
-      <c r="F57" t="s">
-        <v>50</v>
-      </c>
-      <c r="G57" t="s">
-        <v>51</v>
-      </c>
-      <c r="H57" t="s">
-        <v>51</v>
-      </c>
       <c r="I57" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L57" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>159</v>
+        <v>110</v>
+      </c>
+      <c r="E58" s="1">
+        <v>26173</v>
       </c>
       <c r="F58" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>51</v>
+      </c>
+      <c r="H58" t="s">
+        <v>51</v>
       </c>
       <c r="I58" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="J58" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K58" s="2">
-        <v>46324.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>42</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F59" t="s">
-        <v>88</v>
+        <v>45</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J59" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K59" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46324.647916666669</v>
+        <v>46324</v>
       </c>
       <c r="K60" s="2">
-        <v>46326.147916666669</v>
+        <v>46326</v>
       </c>
       <c r="L60" t="s">
         <v>26</v>
@@ -3215,28 +3218,28 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.003472222219</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K61" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L61" t="s">
         <v>26</v>
@@ -3247,28 +3250,28 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F62" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K62" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L62" t="s">
         <v>26</v>
@@ -3276,28 +3279,31 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D63" t="s">
-        <v>102</v>
+        <v>167</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F63" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I63" t="s">
         <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K63" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L63" t="s">
         <v>26</v>
@@ -3305,31 +3311,28 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" t="s">
         <v>32</v>
       </c>
-      <c r="B64" t="s">
-        <v>60</v>
-      </c>
-      <c r="C64" t="s">
-        <v>79</v>
-      </c>
-      <c r="D64" t="s">
-        <v>169</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F64" t="s">
-        <v>45</v>
-      </c>
       <c r="I64" t="s">
         <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K64" s="2">
-        <v>46329.708333333336</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L64" t="s">
         <v>26</v>
@@ -3337,13 +3340,13 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B65" t="s">
         <v>60</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D65" t="s">
         <v>169</v>
@@ -3369,92 +3372,92 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C66" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="D66" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" s="1">
-        <v>26172</v>
+        <v>169</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F66" t="s">
-        <v>50</v>
-      </c>
-      <c r="G66" t="s">
-        <v>51</v>
-      </c>
-      <c r="H66" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
         <v>46325.625</v>
       </c>
       <c r="K66" s="2">
-        <v>46326.041666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L66" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>172</v>
+        <v>49</v>
+      </c>
+      <c r="E67" s="1">
+        <v>26172</v>
       </c>
       <c r="F67" t="s">
-        <v>45</v>
+        <v>50</v>
+      </c>
+      <c r="G67" t="s">
+        <v>51</v>
+      </c>
+      <c r="H67" t="s">
+        <v>51</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -3463,7 +3466,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -3471,42 +3474,39 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F69" t="s">
-        <v>78</v>
-      </c>
-      <c r="G69" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="I69" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
         <v>42</v>
@@ -3515,10 +3515,10 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F70" t="s">
         <v>45</v>
@@ -3527,7 +3527,7 @@
         <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J70" s="2">
         <v>46326.25</v>
@@ -3541,127 +3541,130 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>177</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F71" t="s">
-        <v>37</v>
+        <v>78</v>
+      </c>
+      <c r="G71" t="s">
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K71" s="2">
         <v>46326.75</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>40</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" t="s">
         <v>32</v>
       </c>
-      <c r="B72" t="s">
-        <v>42</v>
-      </c>
-      <c r="C72" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>175</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F72" t="s">
-        <v>78</v>
-      </c>
-      <c r="G72" t="s">
-        <v>18</v>
-      </c>
       <c r="I72" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
-        <v>147</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F73" t="s">
-        <v>181</v>
+        <v>78</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="C74" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="D74" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F74" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -3669,92 +3672,92 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="D75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F75" t="s">
-        <v>45</v>
-      </c>
-      <c r="G75" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L75" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>42</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>186</v>
+        <v>184</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F76" t="s">
-        <v>83</v>
+        <v>45</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J76" s="2">
+        <v>46327.25</v>
+      </c>
+      <c r="K76" s="2">
         <v>46327.708333333336</v>
       </c>
-      <c r="K76" s="2">
-        <v>46328.833333333336</v>
-      </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>90</v>
-      </c>
-      <c r="C77" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F77" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -3762,31 +3765,31 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C78" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D78" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F78" t="s">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46329</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K78" s="2">
-        <v>46330</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L78" t="s">
         <v>26</v>
@@ -3794,147 +3797,147 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F79" t="s">
-        <v>45</v>
-      </c>
-      <c r="G79" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="I79" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46329.25</v>
+        <v>46329</v>
       </c>
       <c r="K79" s="2">
-        <v>46329.75</v>
+        <v>46330</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C80" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F80" t="s">
-        <v>181</v>
+        <v>45</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.333333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K80" s="2">
-        <v>46332.625</v>
+        <v>46329.75</v>
       </c>
       <c r="L80" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D81" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F81" t="s">
-        <v>45</v>
-      </c>
-      <c r="G81" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I81" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.791666666664</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46330.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F82" t="s">
         <v>45</v>
       </c>
+      <c r="G82" t="s">
+        <v>18</v>
+      </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J82" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46334</v>
+        <v>46330.75</v>
       </c>
       <c r="L82" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B83" t="s">
         <v>60</v>
       </c>
       <c r="C83" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D83" t="s">
         <v>195</v>
@@ -3960,28 +3963,31 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="C84" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>195</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="F84" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I84" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K84" s="2">
-        <v>46331.125</v>
+        <v>46334</v>
       </c>
       <c r="L84" t="s">
         <v>26</v>
@@ -3989,31 +3995,28 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
-        <v>197</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>198</v>
+        <v>110</v>
       </c>
       <c r="F85" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K85" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -4021,7 +4024,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B86" t="s">
         <v>60</v>
@@ -4053,28 +4056,31 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C87" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>197</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F87" t="s">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
@@ -4082,31 +4088,28 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="D88" t="s">
-        <v>199</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>200</v>
+        <v>132</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.75</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K88" s="2">
-        <v>46332.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L88" t="s">
         <v>26</v>
@@ -4114,66 +4117,63 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D89" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F89" t="s">
-        <v>78</v>
-      </c>
-      <c r="G89" t="s">
-        <v>18</v>
-      </c>
-      <c r="H89" t="s">
-        <v>203</v>
+        <v>39</v>
       </c>
       <c r="I89" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J89" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K89" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L89" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>204</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
+        <v>201</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F90" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="G90" t="s">
         <v>18</v>
       </c>
+      <c r="H90" t="s">
+        <v>203</v>
+      </c>
       <c r="I90" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J90" s="2">
         <v>46331.25</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B91" t="s">
         <v>54</v>
@@ -4196,19 +4196,19 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1">
         <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G91" t="s">
         <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J91" s="2">
         <v>46331.25</v>
@@ -4222,63 +4222,66 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>206</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
+      </c>
+      <c r="E92" s="1">
+        <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>31</v>
+        <v>94</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K92" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C93" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D93" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="F93" t="s">
-        <v>181</v>
+        <v>39</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -4286,13 +4289,13 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C94" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D94" t="s">
         <v>208</v>
@@ -4318,42 +4321,39 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C95" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="D95" t="s">
-        <v>205</v>
-      </c>
-      <c r="E95" s="1">
-        <v>10</v>
+        <v>208</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F95" t="s">
-        <v>99</v>
-      </c>
-      <c r="G95" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="I95" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L95" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
         <v>42</v>
@@ -4377,7 +4377,7 @@
         <v>203</v>
       </c>
       <c r="I96" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J96" s="2">
         <v>46331.791666666664</v>
@@ -4391,10 +4391,10 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -4403,16 +4403,16 @@
         <v>204</v>
       </c>
       <c r="E97" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G97" t="s">
         <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J97" s="2">
         <v>46331.791666666664</v>
@@ -4426,89 +4426,98 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>209</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>24</v>
+        <v>94</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L98" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>122</v>
       </c>
       <c r="D99" t="s">
-        <v>35</v>
+        <v>209</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L99" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C100" t="s">
+        <v>29</v>
       </c>
       <c r="D100" t="s">
-        <v>211</v>
+        <v>30</v>
       </c>
       <c r="F100" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
       </c>
       <c r="J100" s="2">
-        <v>46332.375</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46333.5</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4522,7 +4531,7 @@
         <v>211</v>
       </c>
       <c r="F101" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4539,30 +4548,56 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" t="s">
+        <v>211</v>
+      </c>
+      <c r="F102" t="s">
+        <v>84</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" s="2">
+        <v>46332.375</v>
+      </c>
+      <c r="K102" s="2">
+        <v>46333.5</v>
+      </c>
+      <c r="L102" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
         <v>47</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" t="s">
         <v>48</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D103" t="s">
         <v>49</v>
       </c>
-      <c r="F102" t="s">
+      <c r="F103" t="s">
         <v>50</v>
       </c>
-      <c r="I102" t="s">
-        <v>19</v>
-      </c>
-      <c r="J102" s="2">
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" s="2">
         <v>46332.541666666664</v>
       </c>
-      <c r="K102" s="2">
+      <c r="K103" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="L102" t="s">
+      <c r="L103" t="s">
         <v>53</v>
       </c>
     </row>

--- a/data/vessels/2026-10-16.xlsx
+++ b/data/vessels/2026-10-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430755" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74E3B2B9-F99C-470E-86DC-67C9D349F6AA}"/>
+  <xr:revisionPtr revIDLastSave="430974" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F5D437D-7C2D-4DFB-B271-E87E61D1CA7C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="211">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,6 +83,27 @@
     <t>T18</t>
   </si>
   <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>Ad Hoc</t>
   </si>
   <si>
@@ -98,28 +119,25 @@
     <t>Norton Lilly International</t>
   </si>
   <si>
-    <t>Container</t>
-  </si>
-  <si>
     <t>Not available</t>
   </si>
   <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>In transit</t>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>CAPE TAINARO</t>
+  </si>
+  <si>
+    <t>MC642R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>At berth</t>
   </si>
   <si>
     <t>Tacoma</t>
@@ -128,399 +146,378 @@
     <t>WST</t>
   </si>
   <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MANULANI</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>IRIS ACE</t>
+  </si>
+  <si>
+    <t>110A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>Waiting 3 days</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
     <t>Matson - AK</t>
   </si>
   <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>193E</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN040S19</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK638A</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>197E</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
     <t>MATSON KODIAK</t>
   </si>
   <si>
-    <t>641S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>At berth</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>CAPE TAINARO</t>
-  </si>
-  <si>
-    <t>MC642R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MANULANI</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>IRIS ACE</t>
-  </si>
-  <si>
-    <t>110A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Waiting 2.7 days</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>193E</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK638A</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>197E</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
     <t>EVER MODE</t>
   </si>
   <si>
@@ -644,6 +641,12 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -651,12 +654,6 @@
   </si>
   <si>
     <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -747,10 +744,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L103" totalsRowShown="0">
-  <autoFilter ref="A1:L103" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L103">
-    <sortCondition ref="J2:J103"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
+  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
+    <sortCondition ref="J2:J102"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1087,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1182,19 +1179,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -1206,7 +1203,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1252,19 +1249,19 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1276,112 +1273,112 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="2">
+        <v>46311.25</v>
+      </c>
+      <c r="K6" s="2">
+        <v>46312.166666666664</v>
+      </c>
+      <c r="L6" t="s">
         <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="2">
-        <v>46311.104166666664</v>
-      </c>
-      <c r="K6" s="2">
-        <v>46311.916666666664</v>
-      </c>
-      <c r="L6" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
       <c r="I7" t="s">
         <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46311.25</v>
+        <v>46311.333333333336</v>
       </c>
       <c r="K7" s="2">
-        <v>46312.166666666664</v>
+        <v>46312.125</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="J8" s="2">
-        <v>46311.333333333336</v>
+        <v>46311.541666666664</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.125</v>
+        <v>46312.083333333336</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -1389,113 +1386,113 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="E9" s="1">
+        <v>26164</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J9" s="2">
-        <v>46311.541666666664</v>
+        <v>46311.625</v>
       </c>
       <c r="K9" s="2">
-        <v>46312.083333333336</v>
+        <v>46312.041666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="1">
-        <v>26164</v>
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J10" s="2">
-        <v>46311.625</v>
+        <v>46312.125</v>
       </c>
       <c r="K10" s="2">
-        <v>46312.041666666664</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46312.125</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46312.666666666664</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L11" t="s">
         <v>20</v>
@@ -1503,75 +1500,72 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K12" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I13" t="s">
         <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46312.3125</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K13" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1591,22 +1585,22 @@
         <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="I14" t="s">
         <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46312.541666666664</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K14" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1614,63 +1608,63 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46313.208333333336</v>
+        <v>46313.25</v>
       </c>
       <c r="K15" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" t="s">
         <v>75</v>
       </c>
-      <c r="F16" t="s">
-        <v>39</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" t="s">
-        <v>19</v>
-      </c>
       <c r="J16" s="2">
-        <v>46313.25</v>
+        <v>46314.25</v>
       </c>
       <c r="K16" s="2">
         <v>46314.75</v>
@@ -1681,13 +1675,13 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>76</v>
@@ -1699,10 +1693,10 @@
         <v>78</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J17" s="2">
         <v>46314.25</v>
@@ -1711,39 +1705,39 @@
         <v>46314.75</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>81</v>
+      <c r="E18" s="1">
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K18" s="2">
-        <v>46314.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1757,19 +1751,19 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" t="s">
         <v>83</v>
       </c>
-      <c r="F19" t="s">
-        <v>84</v>
-      </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
@@ -1781,39 +1775,39 @@
         <v>46315.166666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" t="s">
         <v>85</v>
       </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="1">
-        <v>34</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J20" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K20" s="2">
-        <v>46318.166666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -1821,25 +1815,25 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
         <v>87</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>88</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" t="s">
         <v>90</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>91</v>
-      </c>
-      <c r="G21" t="s">
-        <v>92</v>
       </c>
       <c r="I21" t="s">
         <v>19</v>
@@ -1848,42 +1842,42 @@
         <v>46315.208333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46316.791666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" t="s">
-        <v>54</v>
-      </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E22" s="1">
-        <v>2</v>
-      </c>
       <c r="F22" t="s">
-        <v>94</v>
+        <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46315.541666666664</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K22" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1891,25 +1885,25 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" t="s">
         <v>95</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>96</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="F23" t="s">
         <v>98</v>
       </c>
-      <c r="F23" t="s">
-        <v>99</v>
-      </c>
       <c r="G23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
@@ -1921,39 +1915,42 @@
         <v>46317.75</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
         <v>101</v>
       </c>
-      <c r="F24" t="s">
-        <v>39</v>
-      </c>
-      <c r="G24" t="s">
-        <v>18</v>
-      </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J24" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K24" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -1961,13 +1958,13 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
         <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>103</v>
@@ -1976,13 +1973,13 @@
         <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J25" s="2">
         <v>46316.25</v>
@@ -1991,33 +1988,33 @@
         <v>46316.75</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>104</v>
       </c>
       <c r="D26" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H26" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
@@ -2029,65 +2026,68 @@
         <v>46316.916666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="E27" s="1">
+        <v>26169</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>48</v>
+      </c>
+      <c r="H27" t="s">
+        <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J27" s="2">
         <v>46316.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F28" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I28" t="s">
         <v>19</v>
@@ -2099,59 +2099,56 @@
         <v>46319.75</v>
       </c>
       <c r="L28" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" t="s">
         <v>109</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="1">
-        <v>26169</v>
-      </c>
       <c r="F29" t="s">
-        <v>50</v>
+        <v>111</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
-      </c>
-      <c r="H29" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2">
         <v>46316.625</v>
       </c>
       <c r="K29" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
         <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>112</v>
@@ -2160,13 +2157,13 @@
         <v>78</v>
       </c>
       <c r="G30" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J30" s="2">
         <v>46317.208333333336</v>
@@ -2175,27 +2172,27 @@
         <v>46317.75</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" t="s">
+        <v>90</v>
+      </c>
+      <c r="G31" t="s">
         <v>115</v>
-      </c>
-      <c r="F31" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" t="s">
-        <v>116</v>
       </c>
       <c r="I31" t="s">
         <v>19</v>
@@ -2207,7 +2204,7 @@
         <v>46318.708333333336</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2215,19 +2212,19 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="F32" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I32" t="s">
         <v>19</v>
@@ -2239,33 +2236,33 @@
         <v>46318.166666666664</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>102</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I33" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J33" s="2">
         <v>46317.541666666664</v>
@@ -2274,33 +2271,33 @@
         <v>46320.75</v>
       </c>
       <c r="L33" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G34" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I34" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J34" s="2">
         <v>46317.541666666664</v>
@@ -2309,42 +2306,36 @@
         <v>46320.75</v>
       </c>
       <c r="L34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D35" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F35" t="s">
-        <v>78</v>
-      </c>
-      <c r="G35" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J35" s="2">
-        <v>46317.666666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K35" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -2352,31 +2343,34 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
         <v>123</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="G36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" t="s">
+        <v>38</v>
       </c>
       <c r="I36" t="s">
         <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -2384,48 +2378,48 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="D38" t="s">
         <v>126</v>
@@ -2434,19 +2428,22 @@
         <v>127</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>56</v>
+      </c>
+      <c r="H38" t="s">
+        <v>38</v>
       </c>
       <c r="I38" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2">
         <v>46318.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46318.75</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L38" t="s">
         <v>20</v>
@@ -2454,13 +2451,13 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
         <v>128</v>
@@ -2469,130 +2466,127 @@
         <v>129</v>
       </c>
       <c r="F39" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="H39" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I39" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>131</v>
+        <v>46</v>
+      </c>
+      <c r="E40" s="1">
+        <v>26168</v>
       </c>
       <c r="F40" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H40" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J40" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.125</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="1">
-        <v>26168</v>
+        <v>130</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
-      </c>
-      <c r="G41" t="s">
-        <v>51</v>
-      </c>
-      <c r="H41" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J41" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L41" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" s="1" t="s">
         <v>131</v>
       </c>
+      <c r="E42" s="1">
+        <v>4</v>
+      </c>
       <c r="F42" t="s">
-        <v>32</v>
+        <v>85</v>
+      </c>
+      <c r="G42" t="s">
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J42" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K42" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L42" t="s">
         <v>26</v>
@@ -2600,48 +2594,48 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E43" s="1">
-        <v>4</v>
-      </c>
       <c r="F43" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K43" s="2">
         <v>46319.75</v>
       </c>
       <c r="L43" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D44" t="s">
         <v>134</v>
@@ -2650,54 +2644,54 @@
         <v>135</v>
       </c>
       <c r="F44" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>56</v>
+      </c>
+      <c r="H44" t="s">
+        <v>137</v>
       </c>
       <c r="I44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J44" s="2">
         <v>46319.25</v>
       </c>
       <c r="K44" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="F45" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="G45" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="H45" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="I45" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.25</v>
+        <v>46319.625</v>
       </c>
       <c r="K45" s="2">
         <v>46320.166666666664</v>
@@ -2708,48 +2702,48 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>139</v>
       </c>
       <c r="D46" t="s">
         <v>140</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="F46" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G46" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46319.625</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K46" s="2">
-        <v>46320.166666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C47" t="s">
-        <v>141</v>
+        <v>87</v>
       </c>
       <c r="D47" t="s">
         <v>142</v>
@@ -2758,33 +2752,30 @@
         <v>143</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
-      </c>
-      <c r="G47" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46319.666666666664</v>
+        <v>46320</v>
       </c>
       <c r="K47" s="2">
-        <v>46321.75</v>
+        <v>46322</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
         <v>144</v>
@@ -2793,19 +2784,19 @@
         <v>145</v>
       </c>
       <c r="F48" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46320</v>
+        <v>46320.21875</v>
       </c>
       <c r="K48" s="2">
-        <v>46322</v>
+        <v>46324.59375</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2825,19 +2816,22 @@
         <v>147</v>
       </c>
       <c r="F49" t="s">
-        <v>17</v>
+        <v>68</v>
+      </c>
+      <c r="G49" t="s">
+        <v>69</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46320.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K49" s="2">
-        <v>46324.59375</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2845,10 +2839,10 @@
         <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D50" t="s">
         <v>148</v>
@@ -2857,33 +2851,30 @@
         <v>149</v>
       </c>
       <c r="F50" t="s">
-        <v>71</v>
-      </c>
-      <c r="G50" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.21875</v>
       </c>
       <c r="K50" s="2">
-        <v>46322.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C51" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="D51" t="s">
         <v>150</v>
@@ -2892,86 +2883,89 @@
         <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>98</v>
+      </c>
+      <c r="G51" t="s">
+        <v>56</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.21875</v>
+        <v>46321.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.21875</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
         <v>152</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>153</v>
+      <c r="E52" s="1">
+        <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G52" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="I52" t="s">
         <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46321.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K52" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>154</v>
-      </c>
-      <c r="E53" s="1">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>56</v>
+      </c>
+      <c r="H53" t="s">
+        <v>137</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J53" s="2">
-        <v>46321.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
@@ -2979,34 +2973,34 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D54" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>155</v>
       </c>
       <c r="F54" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="G54" t="s">
-        <v>59</v>
-      </c>
-      <c r="H54" t="s">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46322.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K54" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
@@ -3014,13 +3008,13 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
         <v>156</v>
@@ -3029,19 +3023,19 @@
         <v>157</v>
       </c>
       <c r="F55" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J55" s="2">
-        <v>46322.625</v>
+        <v>46323.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46325.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L55" t="s">
         <v>26</v>
@@ -3049,63 +3043,66 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D56" t="s">
         <v>158</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="F56" t="s">
-        <v>45</v>
-      </c>
-      <c r="G56" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I56" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46323.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="D57" t="s">
-        <v>30</v>
+        <v>108</v>
+      </c>
+      <c r="E57" s="1">
+        <v>26173</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G57" t="s">
+        <v>48</v>
+      </c>
+      <c r="H57" t="s">
+        <v>48</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K57" s="2">
-        <v>46323.791666666664</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -3113,37 +3110,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
-      </c>
-      <c r="E58" s="1">
-        <v>26173</v>
+        <v>156</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F58" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G58" t="s">
-        <v>51</v>
-      </c>
-      <c r="H58" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="J58" s="2">
-        <v>46323.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46324.041666666664</v>
+        <v>46324.75</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -3151,34 +3145,28 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
-      </c>
-      <c r="G59" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="I59" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46323.791666666664</v>
+        <v>46324</v>
       </c>
       <c r="K59" s="2">
-        <v>46324.75</v>
+        <v>46326</v>
       </c>
       <c r="L59" t="s">
         <v>20</v>
@@ -3186,31 +3174,34 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>161</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F60" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46324</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K60" s="2">
-        <v>46326</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3218,31 +3209,31 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>28</v>
       </c>
       <c r="D61" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F61" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.147916666669</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3250,112 +3241,118 @@
         <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K62" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C63" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="F63" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I63" t="s">
         <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K63" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D64" t="s">
-        <v>104</v>
+        <v>46</v>
+      </c>
+      <c r="E64" s="1">
+        <v>26172</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G64" t="s">
+        <v>48</v>
+      </c>
+      <c r="H64" t="s">
+        <v>48</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J64" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D65" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="F65" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
@@ -3367,27 +3364,27 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D66" t="s">
+        <v>168</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="F66" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
@@ -3399,65 +3396,59 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
-      </c>
-      <c r="E67" s="1">
-        <v>26172</v>
+        <v>170</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F67" t="s">
-        <v>50</v>
-      </c>
-      <c r="G67" t="s">
-        <v>51</v>
-      </c>
-      <c r="H67" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J67" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46326.041666666664</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L67" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
         <v>27</v>
       </c>
-      <c r="B68" t="s">
-        <v>95</v>
-      </c>
       <c r="C68" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F68" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -3466,39 +3457,42 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46328.916666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C69" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="G69" t="s">
+        <v>25</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L69" t="s">
         <v>26</v>
@@ -3506,28 +3500,28 @@
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D70" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F70" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I70" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J70" s="2">
         <v>46326.25</v>
@@ -3536,68 +3530,68 @@
         <v>46326.75</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="F71" t="s">
-        <v>78</v>
-      </c>
-      <c r="G71" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I71" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K71" s="2">
         <v>46326.75</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>41</v>
+        <v>176</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>78</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46326.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L72" t="s">
         <v>26</v>
@@ -3605,34 +3599,31 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F73" t="s">
-        <v>78</v>
-      </c>
-      <c r="G73" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="I73" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46327.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L73" t="s">
         <v>20</v>
@@ -3640,63 +3631,66 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F74" t="s">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D75" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F75" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="G75" t="s">
+        <v>25</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K75" s="2">
-        <v>46328.541666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -3704,34 +3698,25 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>184</v>
-      </c>
-      <c r="E76" s="1" t="s">
         <v>185</v>
       </c>
       <c r="F76" t="s">
-        <v>45</v>
-      </c>
-      <c r="G76" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="I76" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J76" s="2">
-        <v>46327.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K76" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
@@ -3739,89 +3724,98 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>94</v>
+      </c>
+      <c r="C77" t="s">
+        <v>95</v>
       </c>
       <c r="D77" t="s">
         <v>186</v>
       </c>
+      <c r="E77" s="1" t="s">
+        <v>187</v>
+      </c>
       <c r="F77" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K77" s="2">
-        <v>46328.833333333336</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D78" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.904861111114</v>
+        <v>46329</v>
       </c>
       <c r="K78" s="2">
-        <v>46331.196527777778</v>
+        <v>46330</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="C79" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F79" t="s">
-        <v>91</v>
+        <v>42</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J79" s="2">
-        <v>46329</v>
+        <v>46329.25</v>
       </c>
       <c r="K79" s="2">
-        <v>46330</v>
+        <v>46329.75</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -3829,34 +3823,31 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="D80" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F80" t="s">
-        <v>45</v>
-      </c>
-      <c r="G80" t="s">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="I80" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.25</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46329.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
@@ -3864,31 +3855,34 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F81" t="s">
-        <v>181</v>
+        <v>42</v>
+      </c>
+      <c r="G81" t="s">
+        <v>25</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.333333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46332.625</v>
+        <v>46330.75</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -3896,34 +3890,31 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" t="s">
+        <v>194</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F82" t="s">
         <v>42</v>
       </c>
-      <c r="C82" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>191</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F82" t="s">
-        <v>45</v>
-      </c>
-      <c r="G82" t="s">
-        <v>18</v>
-      </c>
       <c r="I82" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K82" s="2">
-        <v>46330.75</v>
+        <v>46334</v>
       </c>
       <c r="L82" t="s">
         <v>20</v>
@@ -3931,22 +3922,22 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>196</v>
-      </c>
       <c r="F83" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
@@ -3958,88 +3949,88 @@
         <v>46334</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="D84" t="s">
-        <v>195</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="F84" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K84" s="2">
-        <v>46334</v>
+        <v>46331.125</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C85" t="s">
-        <v>109</v>
+        <v>58</v>
       </c>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>196</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>197</v>
       </c>
       <c r="F85" t="s">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.625</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K85" s="2">
-        <v>46331.125</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C86" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="F86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
@@ -4051,97 +4042,100 @@
         <v>46333.925000000003</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>197</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>198</v>
+        <v>130</v>
       </c>
       <c r="F87" t="s">
-        <v>181</v>
+        <v>37</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K87" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
         <v>27</v>
       </c>
-      <c r="B88" t="s">
-        <v>28</v>
-      </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>132</v>
+        <v>198</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.75</v>
       </c>
       <c r="K88" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.75</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C89" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D89" t="s">
-        <v>199</v>
-      </c>
-      <c r="E89" s="1" t="s">
         <v>200</v>
       </c>
+      <c r="E89" s="1">
+        <v>10</v>
+      </c>
       <c r="F89" t="s">
-        <v>39</v>
+        <v>85</v>
+      </c>
+      <c r="G89" t="s">
+        <v>25</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.75</v>
+        <v>46331.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46332.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
@@ -4149,31 +4143,28 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D90" t="s">
         <v>201</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>202</v>
+      <c r="E90" s="1">
+        <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G90" t="s">
-        <v>18</v>
-      </c>
-      <c r="H90" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="I90" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J90" s="2">
         <v>46331.25</v>
@@ -4182,33 +4173,36 @@
         <v>46331.75</v>
       </c>
       <c r="L90" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
+        <v>202</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F91" t="s">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s">
+        <v>25</v>
+      </c>
+      <c r="H91" t="s">
         <v>204</v>
       </c>
-      <c r="E91" s="1">
-        <v>10</v>
-      </c>
-      <c r="F91" t="s">
-        <v>94</v>
-      </c>
-      <c r="G91" t="s">
-        <v>18</v>
-      </c>
       <c r="I91" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J91" s="2">
         <v>46331.25</v>
@@ -4217,39 +4211,36 @@
         <v>46331.75</v>
       </c>
       <c r="L91" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
         <v>27</v>
       </c>
-      <c r="B92" t="s">
-        <v>42</v>
-      </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D92" t="s">
         <v>205</v>
       </c>
-      <c r="E92" s="1">
-        <v>1</v>
+      <c r="E92" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F92" t="s">
-        <v>94</v>
-      </c>
-      <c r="G92" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I92" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L92" t="s">
         <v>20</v>
@@ -4257,54 +4248,54 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C93" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="F93" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="I93" t="s">
         <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K93" s="2">
-        <v>46332.166666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
+        <v>94</v>
+      </c>
+      <c r="C94" t="s">
         <v>95</v>
       </c>
-      <c r="C94" t="s">
-        <v>96</v>
-      </c>
       <c r="D94" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F94" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
@@ -4316,36 +4307,42 @@
         <v>46334.746527777781</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C95" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="F95" t="s">
-        <v>181</v>
+        <v>78</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
+      </c>
+      <c r="H95" t="s">
+        <v>204</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -4353,31 +4350,28 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D96" t="s">
         <v>201</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>202</v>
+      <c r="E96" s="1">
+        <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G96" t="s">
-        <v>18</v>
-      </c>
-      <c r="H96" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="I96" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J96" s="2">
         <v>46331.791666666664</v>
@@ -4386,33 +4380,33 @@
         <v>46332.75</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D97" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E97" s="1">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G97" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I97" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="J97" s="2">
         <v>46331.791666666664</v>
@@ -4421,39 +4415,36 @@
         <v>46332.75</v>
       </c>
       <c r="L97" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D98" t="s">
-        <v>205</v>
-      </c>
-      <c r="E98" s="1">
-        <v>1</v>
+        <v>208</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="F98" t="s">
-        <v>94</v>
-      </c>
-      <c r="G98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L98" t="s">
         <v>20</v>
@@ -4461,31 +4452,28 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="D99" t="s">
-        <v>209</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>210</v>
+        <v>158</v>
       </c>
       <c r="F99" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
@@ -4493,28 +4481,25 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
-      </c>
-      <c r="C100" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
       </c>
       <c r="J100" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L100" t="s">
         <v>20</v>
@@ -4528,10 +4513,10 @@
         <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F101" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
@@ -4543,62 +4528,36 @@
         <v>46333.5</v>
       </c>
       <c r="L101" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
       </c>
       <c r="D102" t="s">
-        <v>211</v>
+        <v>46</v>
       </c>
       <c r="F102" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
       </c>
       <c r="J102" s="2">
-        <v>46332.375</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46333.5</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12">
-      <c r="A103" t="s">
-        <v>27</v>
-      </c>
-      <c r="B103" t="s">
-        <v>47</v>
-      </c>
-      <c r="C103" t="s">
-        <v>48</v>
-      </c>
-      <c r="D103" t="s">
-        <v>49</v>
-      </c>
-      <c r="F103" t="s">
         <v>50</v>
-      </c>
-      <c r="I103" t="s">
-        <v>19</v>
-      </c>
-      <c r="J103" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K103" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="L103" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/vessels/2026-10-16.xlsx
+++ b/data/vessels/2026-10-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430974" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F5D437D-7C2D-4DFB-B271-E87E61D1CA7C}"/>
+  <xr:revisionPtr revIDLastSave="431511" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2FDEBD0-8AD3-469F-B41F-1BD6B0249295}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="211">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,6 +83,27 @@
     <t>T18</t>
   </si>
   <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -98,30 +119,9 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
-    <t>Container</t>
-  </si>
-  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
     <t>T5</t>
   </si>
   <si>
@@ -143,438 +143,438 @@
     <t>Tacoma</t>
   </si>
   <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>IRIS ACE</t>
+  </si>
+  <si>
+    <t>110A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>Ro-Ro</t>
+  </si>
+  <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
     <t>WST</t>
   </si>
   <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
     <t>Matson - HI2</t>
   </si>
   <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Waiting 3 days</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>193E</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN040S19</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK638A</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>197E</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>1473-010E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>638N</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC637A</t>
+  </si>
+  <si>
+    <t>NADI CHIEF</t>
+  </si>
+  <si>
+    <t>14E</t>
+  </si>
+  <si>
+    <t>ONE SYNERGY</t>
+  </si>
+  <si>
+    <t>OYNT0002E</t>
+  </si>
+  <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>NBBT0001E</t>
+  </si>
+  <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
+  </si>
+  <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
     <t>MANULANI</t>
   </si>
   <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>IRIS ACE</t>
-  </si>
-  <si>
-    <t>110A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>Waiting 3 days</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>193E</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK638A</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>197E</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>638N</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
-    <t>NADI CHIEF</t>
-  </si>
-  <si>
-    <t>14E</t>
-  </si>
-  <si>
-    <t>ONE SYNERGY</t>
-  </si>
-  <si>
-    <t>OYNT0002E</t>
-  </si>
-  <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
-  </si>
-  <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
     <t>HYUNDAI FORWARD</t>
   </si>
   <si>
@@ -641,19 +641,19 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -744,10 +744,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L102" totalsRowShown="0">
-  <autoFilter ref="A1:L102" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L102">
-    <sortCondition ref="J2:J102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L99" totalsRowShown="0">
+  <autoFilter ref="A1:L99" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L99">
+    <sortCondition ref="J2:J99"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1084,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1214,19 +1214,19 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1238,7 +1238,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1249,19 +1249,19 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
         <v>19</v>
@@ -1273,7 +1273,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1296,7 +1296,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
         <v>19</v>
@@ -1319,66 +1319,69 @@
         <v>34</v>
       </c>
       <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F7" t="s">
         <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>38</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="J7" s="2">
-        <v>46311.333333333336</v>
+        <v>46312.125</v>
       </c>
       <c r="K7" s="2">
-        <v>46312.125</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L7" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
         <v>38</v>
       </c>
       <c r="I8" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46311.541666666664</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46312.083333333336</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L8" t="s">
         <v>26</v>
@@ -1389,72 +1392,66 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="1">
-        <v>26164</v>
+        <v>47</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G9" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2">
-        <v>46311.625</v>
+        <v>46312.3125</v>
       </c>
       <c r="K9" s="2">
-        <v>46312.041666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L9" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46312.125</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46312.666666666664</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L10" t="s">
         <v>26</v>
@@ -1468,42 +1465,39 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46312.208333333336</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -1515,54 +1509,54 @@
         <v>60</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46312.3125</v>
+        <v>46313.25</v>
       </c>
       <c r="K12" s="2">
         <v>46314.75</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
       <c r="J13" s="2">
-        <v>46312.541666666664</v>
+        <v>46314.25</v>
       </c>
       <c r="K13" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
@@ -1570,34 +1564,34 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J14" s="2">
-        <v>46313.208333333336</v>
+        <v>46314.25</v>
       </c>
       <c r="K14" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -1608,34 +1602,34 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H15" t="s">
+        <v>38</v>
       </c>
       <c r="I15" t="s">
         <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46313.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K15" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1643,31 +1637,31 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="E16" s="1">
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K16" s="2">
-        <v>46314.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -1678,34 +1672,34 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J17" s="2">
-        <v>46314.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K17" s="2">
-        <v>46314.75</v>
+        <v>46315.75</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1713,101 +1707,101 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
         <v>79</v>
       </c>
-      <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="1">
-        <v>34</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
       <c r="I18" t="s">
         <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46318.166666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>81</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46314.625</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46315.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
+        <v>85</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K20" s="2">
-        <v>46315.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -1818,31 +1812,34 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>87</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
         <v>89</v>
       </c>
-      <c r="F21" t="s">
-        <v>90</v>
-      </c>
-      <c r="G21" t="s">
-        <v>91</v>
-      </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J21" s="2">
-        <v>46315.208333333336</v>
+        <v>46316.25</v>
       </c>
       <c r="K21" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L21" t="s">
         <v>20</v>
@@ -1850,34 +1847,34 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
+      </c>
+      <c r="E22" s="1">
+        <v>63</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J22" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K22" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1888,34 +1885,37 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
         <v>94</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F23" t="s">
-        <v>98</v>
-      </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>96</v>
+      </c>
+      <c r="H23" t="s">
+        <v>38</v>
       </c>
       <c r="I23" t="s">
         <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46317.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1923,34 +1923,31 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F24" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F24" t="s">
-        <v>78</v>
-      </c>
       <c r="G24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K24" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L24" t="s">
         <v>26</v>
@@ -1961,31 +1958,31 @@
         <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="1">
-        <v>63</v>
+        <v>97</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L25" t="s">
         <v>26</v>
@@ -1996,37 +1993,37 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="1">
+        <v>26169</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" t="s">
         <v>104</v>
       </c>
-      <c r="D26" t="s">
+      <c r="H26" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H26" t="s">
-        <v>38</v>
-      </c>
-      <c r="I26" t="s">
-        <v>19</v>
-      </c>
       <c r="J26" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2034,34 +2031,34 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="1">
-        <v>26169</v>
+        <v>87</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="F27" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J27" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K27" s="2">
-        <v>46317.041666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L27" t="s">
         <v>20</v>
@@ -2072,69 +2069,63 @@
         <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s">
         <v>109</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F28" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28" t="s">
-        <v>25</v>
-      </c>
       <c r="I28" t="s">
         <v>19</v>
       </c>
       <c r="J28" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46319.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46316.625</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46319.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2142,37 +2133,34 @@
         <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
-      </c>
-      <c r="E30" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="I30" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J30" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46317.75</v>
+        <v>46320.75</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2180,28 +2168,31 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>14</v>
       </c>
       <c r="D31" t="s">
+        <v>112</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
+      </c>
+      <c r="F31" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" t="s">
-        <v>90</v>
-      </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J31" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46318.708333333336</v>
+        <v>46320.75</v>
       </c>
       <c r="L31" t="s">
         <v>20</v>
@@ -2212,31 +2203,31 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>114</v>
       </c>
       <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I32" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K32" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2244,34 +2235,34 @@
         <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>25</v>
+        <v>96</v>
+      </c>
+      <c r="H33" t="s">
+        <v>38</v>
       </c>
       <c r="I33" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46320.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2279,34 +2270,34 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
         <v>118</v>
       </c>
-      <c r="E34" s="1">
-        <v>1</v>
+      <c r="E34" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="G34" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J34" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46320.75</v>
+        <v>46318.75</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2317,28 +2308,34 @@
         <v>13</v>
       </c>
       <c r="C35" t="s">
+        <v>40</v>
+      </c>
+      <c r="D35" t="s">
         <v>120</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="F35" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="G35" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" t="s">
+        <v>38</v>
       </c>
       <c r="I35" t="s">
         <v>19</v>
       </c>
       <c r="J35" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2346,19 +2343,22 @@
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
         <v>123</v>
       </c>
+      <c r="E36" s="1" t="s">
+        <v>124</v>
+      </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="G36" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="H36" t="s">
         <v>38</v>
@@ -2367,10 +2367,10 @@
         <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L36" t="s">
         <v>26</v>
@@ -2381,72 +2381,69 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="E37" s="1">
+        <v>26168</v>
       </c>
       <c r="F37" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="G37" t="s">
-        <v>25</v>
+        <v>104</v>
+      </c>
+      <c r="H37" t="s">
+        <v>104</v>
       </c>
       <c r="I37" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.25</v>
+        <v>46318.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46318.75</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G38" t="s">
-        <v>56</v>
-      </c>
-      <c r="H38" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="I38" t="s">
         <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L38" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2457,31 +2454,28 @@
         <v>34</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="E39" s="1">
+        <v>4</v>
+      </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s">
-        <v>37</v>
-      </c>
-      <c r="H39" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.291666666664</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.125</v>
+        <v>46319.75</v>
       </c>
       <c r="L39" t="s">
         <v>20</v>
@@ -2492,37 +2486,34 @@
         <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C40" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
-      </c>
-      <c r="E40" s="1">
-        <v>26168</v>
+        <v>130</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
-      </c>
-      <c r="H40" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J40" s="2">
-        <v>46318.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L40" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2530,28 +2521,34 @@
         <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>134</v>
+      </c>
+      <c r="G41" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" t="s">
+        <v>135</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J41" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.204861111109</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
@@ -2559,34 +2556,34 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="1">
-        <v>4</v>
+        <v>136</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H42" t="s">
+        <v>38</v>
       </c>
       <c r="I42" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.625</v>
       </c>
       <c r="K42" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L42" t="s">
         <v>26</v>
@@ -2597,31 +2594,31 @@
         <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F43" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="I43" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L43" t="s">
         <v>26</v>
@@ -2632,34 +2629,28 @@
         <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D44" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F44" t="s">
-        <v>136</v>
-      </c>
-      <c r="G44" t="s">
-        <v>56</v>
-      </c>
-      <c r="H44" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K44" s="2">
-        <v>46320.166666666664</v>
+        <v>46322</v>
       </c>
       <c r="L44" t="s">
         <v>26</v>
@@ -2672,195 +2663,198 @@
       <c r="B45" t="s">
         <v>13</v>
       </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="F45" t="s">
-        <v>83</v>
-      </c>
-      <c r="G45" t="s">
-        <v>25</v>
-      </c>
-      <c r="H45" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.625</v>
+        <v>46320.21875</v>
       </c>
       <c r="K45" s="2">
-        <v>46320.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="D46" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="G46" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K46" s="2">
-        <v>46321.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F47" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46320</v>
+        <v>46321.21875</v>
       </c>
       <c r="K47" s="2">
-        <v>46322</v>
+        <v>46323.21875</v>
       </c>
       <c r="L47" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D48" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>84</v>
+      </c>
+      <c r="G48" t="s">
+        <v>44</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46320.21875</v>
+        <v>46321.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46324.59375</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
+      </c>
+      <c r="E49" s="1">
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="G49" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.208333333336</v>
+        <v>46321.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46322.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L49" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="C50" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F50" t="s">
-        <v>31</v>
+        <v>134</v>
+      </c>
+      <c r="G50" t="s">
+        <v>44</v>
+      </c>
+      <c r="H50" t="s">
+        <v>135</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.21875</v>
+        <v>46322.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.21875</v>
+        <v>46322.75</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
@@ -2871,34 +2865,34 @@
         <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G51" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L51" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2906,31 +2900,31 @@
         <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" s="1">
-        <v>21</v>
+        <v>155</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="F52" t="s">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="G52" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J52" s="2">
-        <v>46321.625</v>
+        <v>46323.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46325.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
@@ -2941,34 +2935,28 @@
         <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F53" t="s">
-        <v>136</v>
-      </c>
-      <c r="G53" t="s">
-        <v>56</v>
-      </c>
-      <c r="H53" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="I53" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K53" s="2">
-        <v>46322.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2976,34 +2964,37 @@
         <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="D54" t="s">
-        <v>154</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>155</v>
+        <v>102</v>
+      </c>
+      <c r="E54" s="1">
+        <v>26173</v>
       </c>
       <c r="F54" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>104</v>
+      </c>
+      <c r="H54" t="s">
+        <v>104</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="J54" s="2">
-        <v>46322.625</v>
+        <v>46323.625</v>
       </c>
       <c r="K54" s="2">
-        <v>46325.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3011,34 +3002,34 @@
         <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D55" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.25</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.75</v>
+        <v>46324.75</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3046,25 +3037,25 @@
         <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D56" t="s">
         <v>158</v>
       </c>
+      <c r="E56" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="F56" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="I56" t="s">
         <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.291666666664</v>
+        <v>46324</v>
       </c>
       <c r="K56" s="2">
-        <v>46323.791666666664</v>
+        <v>46326</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -3072,72 +3063,63 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>108</v>
-      </c>
-      <c r="E57" s="1">
-        <v>26173</v>
+        <v>161</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
-      </c>
-      <c r="G57" t="s">
-        <v>48</v>
-      </c>
-      <c r="H57" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.625</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.041666666664</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L57" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
-      </c>
-      <c r="G58" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K58" s="2">
-        <v>46324.75</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -3145,127 +3127,133 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>13</v>
+      </c>
+      <c r="C59" t="s">
+        <v>21</v>
       </c>
       <c r="D59" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F59" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46324</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K59" s="2">
-        <v>46326</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L59" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C60" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="D60" t="s">
-        <v>162</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>163</v>
+        <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K60" s="2">
-        <v>46326.147916666669</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>165</v>
+        <v>126</v>
+      </c>
+      <c r="E61" s="1">
+        <v>26172</v>
       </c>
       <c r="F61" t="s">
-        <v>31</v>
+        <v>103</v>
+      </c>
+      <c r="G61" t="s">
+        <v>104</v>
+      </c>
+      <c r="H61" t="s">
+        <v>104</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F62" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.625</v>
       </c>
       <c r="K62" s="2">
-        <v>46326.098611111112</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L62" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3273,13 +3261,16 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>167</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F63" t="s">
         <v>37</v>
@@ -3288,13 +3279,13 @@
         <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46325.833333333336</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3302,69 +3293,63 @@
         <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>45</v>
+        <v>137</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
-      </c>
-      <c r="E64" s="1">
-        <v>26172</v>
+        <v>169</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F64" t="s">
-        <v>47</v>
-      </c>
-      <c r="G64" t="s">
-        <v>48</v>
-      </c>
-      <c r="H64" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I64" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K64" s="2">
-        <v>46326.041666666664</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F65" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46329.708333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3372,28 +3357,31 @@
         <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C66" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F66" t="s">
-        <v>42</v>
+        <v>66</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J66" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L66" t="s">
         <v>20</v>
@@ -3404,28 +3392,31 @@
         <v>33</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="C67" t="s">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="G67" t="s">
+        <v>18</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L67" t="s">
         <v>20</v>
@@ -3433,31 +3424,28 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
       </c>
       <c r="J68" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L68" t="s">
         <v>20</v>
@@ -3468,34 +3456,34 @@
         <v>33</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
+        <v>173</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="F69" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G69" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.25</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46326.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3503,31 +3491,28 @@
         <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C70" t="s">
-        <v>21</v>
+        <v>137</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F70" t="s">
-        <v>78</v>
-      </c>
-      <c r="G70" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="I70" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K70" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L70" t="s">
         <v>26</v>
@@ -3535,28 +3520,31 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>181</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="F71" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
         <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K71" s="2">
-        <v>46326.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L71" t="s">
         <v>26</v>
@@ -3567,98 +3555,92 @@
         <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F72" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.791666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K72" s="2">
-        <v>46327.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>94</v>
-      </c>
-      <c r="C73" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F73" t="s">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="I73" t="s">
         <v>19</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L73" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F74" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46327.166666666664</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K74" s="2">
-        <v>46328.541666666664</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3666,31 +3648,28 @@
         <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="D75" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F75" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="I75" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.25</v>
+        <v>46329</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.708333333336</v>
+        <v>46330</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -3698,25 +3677,34 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="F76" t="s">
-        <v>83</v>
+        <v>37</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J76" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46328.833333333336</v>
+        <v>46329.75</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
@@ -3727,31 +3715,31 @@
         <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="D77" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F77" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46331.196527777778</v>
+        <v>46332.625</v>
       </c>
       <c r="L77" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3759,28 +3747,31 @@
         <v>33</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F78" t="s">
-        <v>90</v>
+        <v>37</v>
+      </c>
+      <c r="G78" t="s">
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J78" s="2">
-        <v>46329</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46330</v>
+        <v>46330.75</v>
       </c>
       <c r="L78" t="s">
         <v>20</v>
@@ -3791,31 +3782,28 @@
         <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D79" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F79" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I79" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46329.25</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46329.75</v>
+        <v>46334</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -3826,31 +3814,31 @@
         <v>33</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C80" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F80" t="s">
-        <v>180</v>
+        <v>37</v>
       </c>
       <c r="I80" t="s">
         <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46332.625</v>
+        <v>46334</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3858,31 +3846,25 @@
         <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="C81" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="D81" t="s">
-        <v>190</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>191</v>
+        <v>102</v>
       </c>
       <c r="F81" t="s">
-        <v>42</v>
-      </c>
-      <c r="G81" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="I81" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.625</v>
       </c>
       <c r="K81" s="2">
-        <v>46330.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L81" t="s">
         <v>26</v>
@@ -3893,31 +3875,31 @@
         <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C82" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D82" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F82" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="I82" t="s">
         <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K82" s="2">
-        <v>46334</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L82" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3925,31 +3907,31 @@
         <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C83" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="D83" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F83" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K83" s="2">
-        <v>46334</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L83" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3957,60 +3939,60 @@
         <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F84" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="I84" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.625</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K84" s="2">
-        <v>46331.125</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
         <v>58</v>
       </c>
       <c r="D85" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F85" t="s">
-        <v>180</v>
+        <v>31</v>
       </c>
       <c r="I85" t="s">
         <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.75</v>
       </c>
       <c r="K85" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.75</v>
       </c>
       <c r="L85" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4018,28 +4000,34 @@
         <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="D86" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F86" t="s">
-        <v>180</v>
+        <v>66</v>
+      </c>
+      <c r="G86" t="s">
+        <v>18</v>
+      </c>
+      <c r="H86" t="s">
+        <v>202</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K86" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L86" t="s">
         <v>20</v>
@@ -4053,22 +4041,28 @@
         <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>203</v>
+      </c>
+      <c r="E87" s="1">
+        <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>37</v>
+        <v>73</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.75</v>
       </c>
       <c r="L87" t="s">
         <v>20</v>
@@ -4076,31 +4070,34 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="C88" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>198</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
+      </c>
+      <c r="E88" s="1">
+        <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>31</v>
+        <v>73</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.75</v>
+        <v>46331.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46332.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L88" t="s">
         <v>20</v>
@@ -4108,34 +4105,31 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C89" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D89" t="s">
-        <v>200</v>
-      </c>
-      <c r="E89" s="1">
-        <v>10</v>
+        <v>205</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F89" t="s">
-        <v>85</v>
-      </c>
-      <c r="G89" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I89" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J89" s="2">
-        <v>46331.25</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K89" s="2">
-        <v>46331.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L89" t="s">
         <v>26</v>
@@ -4146,31 +4140,28 @@
         <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D90" t="s">
-        <v>201</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
+        <v>207</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="F90" t="s">
-        <v>85</v>
-      </c>
-      <c r="G90" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="I90" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J90" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K90" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L90" t="s">
         <v>26</v>
@@ -4181,34 +4172,28 @@
         <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D91" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>78</v>
-      </c>
-      <c r="G91" t="s">
-        <v>25</v>
-      </c>
-      <c r="H91" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="I91" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K91" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L91" t="s">
         <v>26</v>
@@ -4216,31 +4201,34 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>151</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>205</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
+      </c>
+      <c r="E92" s="1">
+        <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>31</v>
+        <v>73</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L92" t="s">
         <v>20</v>
@@ -4251,28 +4239,31 @@
         <v>33</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="C93" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>207</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>167</v>
+        <v>204</v>
+      </c>
+      <c r="E93" s="1">
+        <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>180</v>
+        <v>73</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
       </c>
       <c r="I93" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L93" t="s">
         <v>20</v>
@@ -4283,28 +4274,34 @@
         <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="C94" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="F94" t="s">
-        <v>180</v>
+        <v>66</v>
+      </c>
+      <c r="G94" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94" t="s">
+        <v>202</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L94" t="s">
         <v>20</v>
@@ -4312,37 +4309,31 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F95" t="s">
-        <v>78</v>
-      </c>
-      <c r="G95" t="s">
-        <v>25</v>
-      </c>
-      <c r="H95" t="s">
-        <v>204</v>
+        <v>24</v>
       </c>
       <c r="I95" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.75</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -4353,66 +4344,51 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C96" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="D96" t="s">
-        <v>201</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="F96" t="s">
-        <v>85</v>
-      </c>
-      <c r="G96" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="I96" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L96" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>200</v>
-      </c>
-      <c r="E97" s="1">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F97" t="s">
-        <v>85</v>
-      </c>
-      <c r="G97" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="I97" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K97" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L97" t="s">
         <v>26</v>
@@ -4425,29 +4401,23 @@
       <c r="B98" t="s">
         <v>13</v>
       </c>
-      <c r="C98" t="s">
-        <v>120</v>
-      </c>
       <c r="D98" t="s">
-        <v>208</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F98" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I98" t="s">
         <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.375</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.5</v>
       </c>
       <c r="L98" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4455,109 +4425,28 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="D99" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.791666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L99" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12">
-      <c r="A100" t="s">
-        <v>12</v>
-      </c>
-      <c r="B100" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" t="s">
-        <v>210</v>
-      </c>
-      <c r="F100" t="s">
-        <v>83</v>
-      </c>
-      <c r="I100" t="s">
-        <v>19</v>
-      </c>
-      <c r="J100" s="2">
-        <v>46332.375</v>
-      </c>
-      <c r="K100" s="2">
-        <v>46333.5</v>
-      </c>
-      <c r="L100" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12">
-      <c r="A101" t="s">
-        <v>12</v>
-      </c>
-      <c r="B101" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" t="s">
-        <v>210</v>
-      </c>
-      <c r="F101" t="s">
-        <v>83</v>
-      </c>
-      <c r="I101" t="s">
-        <v>19</v>
-      </c>
-      <c r="J101" s="2">
-        <v>46332.375</v>
-      </c>
-      <c r="K101" s="2">
-        <v>46333.5</v>
-      </c>
-      <c r="L101" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12">
-      <c r="A102" t="s">
-        <v>33</v>
-      </c>
-      <c r="B102" t="s">
-        <v>44</v>
-      </c>
-      <c r="C102" t="s">
-        <v>45</v>
-      </c>
-      <c r="D102" t="s">
-        <v>46</v>
-      </c>
-      <c r="F102" t="s">
-        <v>47</v>
-      </c>
-      <c r="I102" t="s">
-        <v>19</v>
-      </c>
-      <c r="J102" s="2">
-        <v>46332.541666666664</v>
-      </c>
-      <c r="K102" s="2">
-        <v>46333.041666666664</v>
-      </c>
-      <c r="L102" t="s">
-        <v>50</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -4569,15 +4458,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -4585,13 +4465,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -4729,18 +4609,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>